--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 122 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 303 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 303 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 122 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve</t>
+          <t>loyer_estime · rendement_anormalement_eleve · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve · surface_a_ventiler · occupation_a_confirmer</t>
+          <t>loyer_estime · rendement_anormalement_eleve · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>A 50 m de la mairie de Colombes, donnant directement sur la place du marché et dans un environnement commerçant mixte (crèche, cabinets médicaux, antiquaire), GROUPE BABYLONE vous propose un local commercial en état d'usage. La surface dispose d'un beau linéaire de vitrine de 11,50mètres. A visiter sans tarder. Restauration interdite. QUARTIER MAIRIE-CENTRE GROUPE BABYLONE vous propose: PRESTATIONS IMMEUBLE : Gardiennage Double accès Aire de chargement Chauffage immeuble gaz Locaux en bon état PRESTATIONS LOT(S) : Entrée par la place du marché Locaux nécessitant une rénovation au goût du jour Linéaire de vitrine : 11,50m Belle hauteur sous plafond Faux plafonds Chauffage collectif au gaz Plinthes et câblage RJ45 CONFIGURATION LOT(S) : RDC : 3 bureaux Mezzanine Sous-sol partiellement aménagé en bureaux, espace cuisine, double sanitaire Sous-sol partiellement laissé en espace de stockage, bénéficiant d'une belle hauteur sous-plafond (4,5m) et d'une aire de livraison pour véhicules légers. Surface RDC : 86,95 m²</t>
+          <t>A 50 m de la mairie de Colombes, donnant directement sur la place du marché et dans un environnement commerçant mixte (crèche, cabinets médicaux, antiquaire), GROUPE BABYLONE vous propose un local commercial en état d'usage. La surface dispose d'un beau linéaire de vitrine de 11,50mètres. A visiter sans tarder. Restauration interdite. QUARTIER MAIRIE-CENTRE</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 040 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 024 €/mois.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>3868.33</v>
+        <v>3850</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>ce bien est 48 % SOUS la médiane locale</t>
+          <t>ce bien est 47 % SOUS la médiane locale</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve · occupation_a_confirmer</t>
+          <t>loyer_estime · rendement_anormalement_eleve · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-colombes-25b6144e.xlsx
+++ b/docs/dossiers/dossier-colombes-25b6144e.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
